--- a/artfynd/A 30053-2024 artfynd.xlsx
+++ b/artfynd/A 30053-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899858</v>
       </c>
       <c r="B2" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899859</v>
       </c>
       <c r="B3" t="n">
-        <v>80185</v>
+        <v>80189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30053-2024 artfynd.xlsx
+++ b/artfynd/A 30053-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899858</v>
       </c>
       <c r="B2" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899859</v>
       </c>
       <c r="B3" t="n">
-        <v>80189</v>
+        <v>80094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30053-2024 artfynd.xlsx
+++ b/artfynd/A 30053-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899858</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899859</v>
       </c>
       <c r="B3" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30053-2024 artfynd.xlsx
+++ b/artfynd/A 30053-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899858</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899859</v>
       </c>
       <c r="B3" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30053-2024 artfynd.xlsx
+++ b/artfynd/A 30053-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899858</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899859</v>
       </c>
       <c r="B3" t="n">
-        <v>80104</v>
+        <v>80106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30053-2024 artfynd.xlsx
+++ b/artfynd/A 30053-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899858</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899859</v>
       </c>
       <c r="B3" t="n">
-        <v>80106</v>
+        <v>80108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30053-2024 artfynd.xlsx
+++ b/artfynd/A 30053-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899858</v>
       </c>
       <c r="B2" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899859</v>
       </c>
       <c r="B3" t="n">
-        <v>80108</v>
+        <v>80109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30053-2024 artfynd.xlsx
+++ b/artfynd/A 30053-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899858</v>
+        <v>128899872</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575745</v>
+        <v>575923</v>
       </c>
       <c r="R2" t="n">
-        <v>6979685</v>
+        <v>6979644</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,48 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899859</v>
+        <v>128899888</v>
       </c>
       <c r="B3" t="n">
-        <v>80109</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Digerlemmen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575745</v>
+        <v>575973</v>
       </c>
       <c r="R3" t="n">
-        <v>6979685</v>
+        <v>6979752</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,21 +854,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -884,6 +866,900 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128899873</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Digerlemmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>575924</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6979661</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128899889</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Digerlemmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>575983</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6979748</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128899884</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Digerlemmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>575955</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6979752</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128899861</v>
+      </c>
+      <c r="B7" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Digerlemmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>575790</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6979680</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128899891</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Digerlemmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>575996</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6979749</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128899856</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Digerlemmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>575719</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6979689</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128899858</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Digerlemmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>575745</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6979685</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128899874</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79583</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Digerlemmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>575932</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6979669</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128899859</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Digerlemmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>575745</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6979685</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30053-2024 artfynd.xlsx
+++ b/artfynd/A 30053-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899872</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899888</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899873</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899889</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899884</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899861</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899891</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1451,6 +1491,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899856</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1548,6 +1593,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899858</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1645,6 +1695,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899874</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1760,8 +1815,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899859</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>